--- a/table_from_link/31497858_table2.xlsx
+++ b/table_from_link/31497858_table2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="awz206-T2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,242 +413,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Gene | Gene</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Males | Beta</t>
+          <t>Males</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Males | P</t>
+          <t>Males</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Females | Beta</t>
+          <t>Females</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Females | P</t>
+          <t>Females</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Sex interaction | Beta</t>
+          <t>Sex interaction</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Sex interaction | P</t>
+          <t>Sex interaction</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGR2</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>−2.069</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.59</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>−0.824</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.263</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.76</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AHR</t>
+          <t>AGR2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>−0.233</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.42</v>
+          <t>−2.069</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>−0.824</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.420</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>0.21</v>
+          <t>1.263</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANKMY2</t>
+          <t>AHR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>−0.037</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.22</v>
+          <t>−0.233</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>−0.078</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.93×10−4</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>−0.041</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.28</v>
+          <t>0.420</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BZW2</t>
+          <t>ANKMY2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>−0.027</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.48</v>
+          <t>−0.037</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>−0.093</t>
+          <t>−0.078</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.02×10−3</t>
+          <t>9.93×10 −4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>−0.064</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.18</v>
+          <t>−0.041</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ISPD</t>
+          <t>BZW2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>−0.395</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.18</v>
+          <t>−0.027</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>−0.537</t>
+          <t>−0.093</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2.02×10 −3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>−0.145</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7</v>
+          <t>−0.064</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>ISPD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>−0.395</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>−0.537</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>−0.145</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TSPAN13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>−0.001</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>−0.010</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.049</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>−0.010</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.3</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
       </c>
     </row>
   </sheetData>
